--- a/data-source/COMPRASQUIMICOS.xlsx
+++ b/data-source/COMPRASQUIMICOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A87165D6-8DD7-4C3E-B395-713FA98E4A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64F101C-86C4-47A2-AE7F-5B799B46F906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Planilha!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -62,6 +75,12 @@
   </si>
   <si>
     <t>PIGMENTO HP-H300S YELLOW CHINA</t>
+  </si>
+  <si>
+    <t>SOLVENTE DMF (NACIONAL)</t>
+  </si>
+  <si>
+    <t>SOLVENTE</t>
   </si>
 </sst>
 </file>
@@ -70,8 +89,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[Blue]###########0;[Red]\-###########0"/>
-    <numFmt numFmtId="166" formatCode="[Blue]###,###,###,##0.000;[Red]\-###,###,###,##0.000"/>
-    <numFmt numFmtId="167" formatCode="[Blue]###,###,###,##0.0000;[Red]\-###,###,###,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="[Blue]###,###,###,##0.000;[Red]\-###,###,###,##0.000"/>
+    <numFmt numFmtId="166" formatCode="[Blue]###,###,###,##0.0000;[Red]\-###,###,###,##0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -133,8 +152,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -473,7 +492,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
@@ -642,6 +661,162 @@
         <v>46344</v>
       </c>
     </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>1042</v>
+      </c>
+      <c r="B7" s="3">
+        <v>8329</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="4">
+        <v>950</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="H7" s="6">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1042</v>
+      </c>
+      <c r="B8" s="3">
+        <v>8329</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2850</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="H8" s="6">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>1617</v>
+      </c>
+      <c r="B9" s="3">
+        <v>8329</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="4">
+        <v>2850</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1.75</v>
+      </c>
+      <c r="H9" s="6">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>1617</v>
+      </c>
+      <c r="B10" s="3">
+        <v>8329</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2850</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1.75</v>
+      </c>
+      <c r="H10" s="6">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>1617</v>
+      </c>
+      <c r="B11" s="3">
+        <v>8329</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4">
+        <v>2850</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1.75</v>
+      </c>
+      <c r="H11" s="6">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>1617</v>
+      </c>
+      <c r="B12" s="3">
+        <v>8329</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="3">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="4">
+        <v>3800</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1.75</v>
+      </c>
+      <c r="H12" s="6">
+        <v>46366</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-source/COMPRASQUIMICOS.xlsx
+++ b/data-source/COMPRASQUIMICOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64F101C-86C4-47A2-AE7F-5B799B46F906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{A87165D6-8DD7-4C3E-B395-713FA98E4A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A0EB409-91F3-4CD9-A584-B9C842240C52}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>SOLVENTE</t>
+  </si>
+  <si>
+    <t>HC2160 PIGMENT</t>
   </si>
 </sst>
 </file>
@@ -492,7 +495,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
@@ -548,7 +551,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="4">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="G2" s="5">
         <v>2.14</v>
@@ -574,7 +577,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="4">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="G3" s="5">
         <v>1.86</v>
@@ -600,7 +603,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="4">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="G4" s="5">
         <v>2.23</v>
@@ -611,7 +614,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>1352</v>
+        <v>1667</v>
       </c>
       <c r="B5" s="3">
         <v>11849</v>
@@ -626,44 +629,44 @@
         <v>10</v>
       </c>
       <c r="F5" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G5" s="5">
-        <v>24.78</v>
+        <v>33</v>
       </c>
       <c r="H5" s="6">
-        <v>46176</v>
+        <v>46344</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>1667</v>
+        <v>1617</v>
       </c>
       <c r="B6" s="3">
-        <v>11849</v>
+        <v>8329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D6" s="3">
         <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F6" s="4">
-        <v>100</v>
+        <v>2850</v>
       </c>
       <c r="G6" s="5">
-        <v>33</v>
+        <v>1.75</v>
       </c>
       <c r="H6" s="6">
-        <v>46344</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>1042</v>
+        <v>1617</v>
       </c>
       <c r="B7" s="3">
         <v>8329</v>
@@ -678,18 +681,18 @@
         <v>14</v>
       </c>
       <c r="F7" s="4">
-        <v>950</v>
+        <v>2850</v>
       </c>
       <c r="G7" s="5">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="H7" s="6">
-        <v>46295</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>1042</v>
+        <v>1617</v>
       </c>
       <c r="B8" s="3">
         <v>8329</v>
@@ -707,10 +710,10 @@
         <v>2850</v>
       </c>
       <c r="G8" s="5">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="H8" s="6">
-        <v>46265</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -730,13 +733,13 @@
         <v>14</v>
       </c>
       <c r="F9" s="4">
-        <v>2850</v>
+        <v>3800</v>
       </c>
       <c r="G9" s="5">
         <v>1.75</v>
       </c>
       <c r="H9" s="6">
-        <v>46294</v>
+        <v>46366</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -744,77 +747,103 @@
         <v>1617</v>
       </c>
       <c r="B10" s="3">
-        <v>8329</v>
+        <v>30218</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3">
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F10" s="4">
-        <v>2850</v>
+        <v>100</v>
       </c>
       <c r="G10" s="5">
-        <v>1.75</v>
+        <v>33</v>
       </c>
       <c r="H10" s="6">
-        <v>46325</v>
+        <v>46367</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>1617</v>
-      </c>
-      <c r="B11" s="3">
-        <v>8329</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="3">
-        <v>9</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
+      <c r="A11">
+        <v>1250</v>
+      </c>
+      <c r="B11">
+        <v>4478</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
       </c>
       <c r="F11" s="4">
-        <v>2850</v>
-      </c>
-      <c r="G11" s="5">
-        <v>1.75</v>
+        <v>1000</v>
+      </c>
+      <c r="G11">
+        <v>2.14</v>
       </c>
       <c r="H11" s="6">
-        <v>46356</v>
+        <v>46368</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>1617</v>
-      </c>
-      <c r="B12" s="3">
-        <v>8329</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="3">
-        <v>9</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>14</v>
+      <c r="A12">
+        <v>1250</v>
+      </c>
+      <c r="B12">
+        <v>5797</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
       </c>
       <c r="F12" s="4">
-        <v>3800</v>
-      </c>
-      <c r="G12" s="5">
-        <v>1.75</v>
+        <v>1000</v>
+      </c>
+      <c r="G12">
+        <v>1.86</v>
       </c>
       <c r="H12" s="6">
-        <v>46366</v>
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1250</v>
+      </c>
+      <c r="B13">
+        <v>6506</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G13">
+        <v>2.23</v>
+      </c>
+      <c r="H13" s="6">
+        <v>46370</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/COMPRASQUIMICOS.xlsx
+++ b/data-source/COMPRASQUIMICOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\QUIMICOS-ANALISE\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{A87165D6-8DD7-4C3E-B395-713FA98E4A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A0EB409-91F3-4CD9-A584-B9C842240C52}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCB827F-A5E2-4C6A-9C41-8C6387F797EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -84,6 +84,57 @@
   </si>
   <si>
     <t>HC2160 PIGMENT</t>
+  </si>
+  <si>
+    <t>RESINA LX-50B (AMERICA ASIA)</t>
+  </si>
+  <si>
+    <t>RESINA IMPORTADA</t>
+  </si>
+  <si>
+    <t>RESINA LR206M-3 (AMERICA ASIA)</t>
+  </si>
+  <si>
+    <t>RESINA LR-02 (AMERICA ASIA)</t>
+  </si>
+  <si>
+    <t>RESINA 699A (AMERICA ASIA)</t>
+  </si>
+  <si>
+    <t>RESINA LX-30B (AMERICA ASIA)</t>
+  </si>
+  <si>
+    <t>RESINA FU6080 (AMERICA ASIA)</t>
+  </si>
+  <si>
+    <t>RESINA F9209A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>RESINA JF-HSY-BY100 - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>RESINA JF-HSY-BY400 - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>RESINA JF-HSY-FP002 - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>RESINA F9207A-1 - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>RESINA SK52 - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>RESINA N5015 - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>RESINA 8050A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>RESINA 8030A - AMERICA ASIA</t>
   </si>
 </sst>
 </file>
@@ -495,7 +546,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
@@ -759,7 +810,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="4">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G10" s="5">
         <v>33</v>
@@ -844,6 +895,396 @@
       </c>
       <c r="H13" s="6">
         <v>46370</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B14" s="3">
+        <v>11370</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="3">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="4">
+        <v>6660</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1.97</v>
+      </c>
+      <c r="H14" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B15" s="3">
+        <v>11374</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3">
+        <v>9</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3060</v>
+      </c>
+      <c r="G15" s="5">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H15" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B16" s="3">
+        <v>11379</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="3">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="4">
+        <v>3060</v>
+      </c>
+      <c r="G16" s="5">
+        <v>5.13</v>
+      </c>
+      <c r="H16" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B17" s="3">
+        <v>11380</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="3">
+        <v>9</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="4">
+        <v>3060</v>
+      </c>
+      <c r="G17" s="5">
+        <v>3.13</v>
+      </c>
+      <c r="H17" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B18" s="3">
+        <v>16336</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="3">
+        <v>9</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="4">
+        <v>5040</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1.97</v>
+      </c>
+      <c r="H18" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B19" s="3">
+        <v>16684</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="3">
+        <v>9</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1080</v>
+      </c>
+      <c r="G19" s="5">
+        <v>2.16</v>
+      </c>
+      <c r="H19" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B20" s="3">
+        <v>40032</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="3">
+        <v>9</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="4">
+        <v>190</v>
+      </c>
+      <c r="G20" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="H20" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B21" s="3">
+        <v>40033</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="3">
+        <v>9</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="4">
+        <v>5</v>
+      </c>
+      <c r="G21" s="5">
+        <v>13.39</v>
+      </c>
+      <c r="H21" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B22" s="3">
+        <v>40034</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="3">
+        <v>9</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4">
+        <v>5</v>
+      </c>
+      <c r="G22" s="5">
+        <v>13.33</v>
+      </c>
+      <c r="H22" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B23" s="3">
+        <v>40035</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="3">
+        <v>9</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="4">
+        <v>5</v>
+      </c>
+      <c r="G23" s="5">
+        <v>21</v>
+      </c>
+      <c r="H23" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B24" s="3">
+        <v>40036</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="3">
+        <v>9</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="4">
+        <v>190</v>
+      </c>
+      <c r="G24" s="5">
+        <v>3.52</v>
+      </c>
+      <c r="H24" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B25" s="3">
+        <v>40037</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="3">
+        <v>9</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4">
+        <v>190</v>
+      </c>
+      <c r="G25" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="H25" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B26" s="3">
+        <v>40038</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="3">
+        <v>9</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4">
+        <v>200</v>
+      </c>
+      <c r="G26" s="5">
+        <v>2.54</v>
+      </c>
+      <c r="H26" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B27" s="3">
+        <v>40039</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="3">
+        <v>9</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="4">
+        <v>200</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="H27" s="6">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B28" s="3">
+        <v>40040</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="3">
+        <v>9</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="4">
+        <v>200</v>
+      </c>
+      <c r="G28" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="H28" s="6">
+        <v>46371</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/COMPRASQUIMICOS.xlsx
+++ b/data-source/COMPRASQUIMICOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\QUIMICOS-ANALISE\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCB827F-A5E2-4C6A-9C41-8C6387F797EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5315D4-564D-431E-87FA-B056E0B89317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -546,7 +546,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
@@ -587,13 +587,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>1250</v>
+        <v>1667</v>
       </c>
       <c r="B2" s="3">
-        <v>4478</v>
+        <v>11849</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3">
         <v>9</v>
@@ -602,91 +602,91 @@
         <v>10</v>
       </c>
       <c r="F2" s="4">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="G2" s="5">
-        <v>2.14</v>
+        <v>33</v>
       </c>
       <c r="H2" s="6">
-        <v>46185</v>
+        <v>46344</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>1250</v>
+        <v>1617</v>
       </c>
       <c r="B3" s="3">
-        <v>5797</v>
+        <v>8329</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3">
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F3" s="4">
-        <v>800</v>
+        <v>2850</v>
       </c>
       <c r="G3" s="5">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="H3" s="6">
-        <v>46185</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>1250</v>
+        <v>1617</v>
       </c>
       <c r="B4" s="3">
-        <v>6506</v>
+        <v>8329</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3">
         <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F4" s="4">
-        <v>800</v>
+        <v>2850</v>
       </c>
       <c r="G4" s="5">
-        <v>2.23</v>
+        <v>1.75</v>
       </c>
       <c r="H4" s="6">
-        <v>46185</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>1667</v>
+        <v>1617</v>
       </c>
       <c r="B5" s="3">
-        <v>11849</v>
+        <v>8329</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F5" s="4">
-        <v>100</v>
+        <v>2850</v>
       </c>
       <c r="G5" s="5">
-        <v>33</v>
+        <v>1.75</v>
       </c>
       <c r="H5" s="6">
-        <v>46344</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -706,13 +706,13 @@
         <v>14</v>
       </c>
       <c r="F6" s="4">
-        <v>2850</v>
+        <v>3800</v>
       </c>
       <c r="G6" s="5">
         <v>1.75</v>
       </c>
       <c r="H6" s="6">
-        <v>46294</v>
+        <v>46366</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -720,181 +720,181 @@
         <v>1617</v>
       </c>
       <c r="B7" s="3">
-        <v>8329</v>
+        <v>30218</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3">
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F7" s="4">
-        <v>2850</v>
+        <v>75</v>
       </c>
       <c r="G7" s="5">
-        <v>1.75</v>
+        <v>33</v>
       </c>
       <c r="H7" s="6">
-        <v>46325</v>
+        <v>46367</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>1617</v>
-      </c>
-      <c r="B8" s="3">
-        <v>8329</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="3">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>14</v>
+      <c r="A8">
+        <v>1250</v>
+      </c>
+      <c r="B8">
+        <v>4478</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
       </c>
       <c r="F8" s="4">
-        <v>2850</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1.75</v>
+        <v>1000</v>
+      </c>
+      <c r="G8">
+        <v>2.14</v>
       </c>
       <c r="H8" s="6">
-        <v>46356</v>
+        <v>46368</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>1617</v>
-      </c>
-      <c r="B9" s="3">
-        <v>8329</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="3">
-        <v>9</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>14</v>
+      <c r="A9">
+        <v>1250</v>
+      </c>
+      <c r="B9">
+        <v>5797</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
       </c>
       <c r="F9" s="4">
-        <v>3800</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1.75</v>
+        <v>1000</v>
+      </c>
+      <c r="G9">
+        <v>1.86</v>
       </c>
       <c r="H9" s="6">
-        <v>46366</v>
+        <v>46369</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>1617</v>
-      </c>
-      <c r="B10" s="3">
-        <v>30218</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="3">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="A10">
+        <v>1250</v>
+      </c>
+      <c r="B10">
+        <v>6506</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="4">
-        <v>75</v>
-      </c>
-      <c r="G10" s="5">
-        <v>33</v>
+        <v>1000</v>
+      </c>
+      <c r="G10">
+        <v>2.23</v>
       </c>
       <c r="H10" s="6">
-        <v>46367</v>
+        <v>46370</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1250</v>
-      </c>
-      <c r="B11">
-        <v>4478</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
+      <c r="A11" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B11" s="3">
+        <v>11370</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="3">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F11" s="4">
-        <v>1000</v>
-      </c>
-      <c r="G11">
-        <v>2.14</v>
+        <v>6660</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1.97</v>
       </c>
       <c r="H11" s="6">
-        <v>46368</v>
+        <v>46371</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>1250</v>
-      </c>
-      <c r="B12">
-        <v>5797</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
+      <c r="A12" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B12" s="3">
+        <v>11374</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="3">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F12" s="4">
-        <v>1000</v>
-      </c>
-      <c r="G12">
-        <v>1.86</v>
+        <v>3060</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4.9000000000000004</v>
       </c>
       <c r="H12" s="6">
-        <v>46369</v>
+        <v>46371</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>1250</v>
-      </c>
-      <c r="B13">
-        <v>6506</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
+      <c r="A13" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B13" s="3">
+        <v>11379</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="3">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F13" s="4">
-        <v>1000</v>
-      </c>
-      <c r="G13">
-        <v>2.23</v>
+        <v>3060</v>
+      </c>
+      <c r="G13" s="5">
+        <v>5.13</v>
       </c>
       <c r="H13" s="6">
-        <v>46370</v>
+        <v>46371</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -902,10 +902,10 @@
         <v>1768</v>
       </c>
       <c r="B14" s="3">
-        <v>11370</v>
+        <v>11380</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D14" s="3">
         <v>9</v>
@@ -914,10 +914,10 @@
         <v>17</v>
       </c>
       <c r="F14" s="4">
-        <v>6660</v>
+        <v>3060</v>
       </c>
       <c r="G14" s="5">
-        <v>1.97</v>
+        <v>3.13</v>
       </c>
       <c r="H14" s="6">
         <v>46371</v>
@@ -928,10 +928,10 @@
         <v>1768</v>
       </c>
       <c r="B15" s="3">
-        <v>11374</v>
+        <v>16336</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3">
         <v>9</v>
@@ -940,10 +940,10 @@
         <v>17</v>
       </c>
       <c r="F15" s="4">
-        <v>3060</v>
+        <v>5040</v>
       </c>
       <c r="G15" s="5">
-        <v>4.9000000000000004</v>
+        <v>1.97</v>
       </c>
       <c r="H15" s="6">
         <v>46371</v>
@@ -954,10 +954,10 @@
         <v>1768</v>
       </c>
       <c r="B16" s="3">
-        <v>11379</v>
+        <v>16684</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D16" s="3">
         <v>9</v>
@@ -966,10 +966,10 @@
         <v>17</v>
       </c>
       <c r="F16" s="4">
-        <v>3060</v>
+        <v>1080</v>
       </c>
       <c r="G16" s="5">
-        <v>5.13</v>
+        <v>2.16</v>
       </c>
       <c r="H16" s="6">
         <v>46371</v>
@@ -980,10 +980,10 @@
         <v>1768</v>
       </c>
       <c r="B17" s="3">
-        <v>11380</v>
+        <v>40032</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D17" s="3">
         <v>9</v>
@@ -992,10 +992,10 @@
         <v>17</v>
       </c>
       <c r="F17" s="4">
-        <v>3060</v>
+        <v>190</v>
       </c>
       <c r="G17" s="5">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="H17" s="6">
         <v>46371</v>
@@ -1006,22 +1006,22 @@
         <v>1768</v>
       </c>
       <c r="B18" s="3">
-        <v>16336</v>
+        <v>40033</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D18" s="3">
         <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F18" s="4">
-        <v>5040</v>
+        <v>5</v>
       </c>
       <c r="G18" s="5">
-        <v>1.97</v>
+        <v>13.39</v>
       </c>
       <c r="H18" s="6">
         <v>46371</v>
@@ -1032,22 +1032,22 @@
         <v>1768</v>
       </c>
       <c r="B19" s="3">
-        <v>16684</v>
+        <v>40034</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D19" s="3">
         <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F19" s="4">
-        <v>1080</v>
+        <v>5</v>
       </c>
       <c r="G19" s="5">
-        <v>2.16</v>
+        <v>13.33</v>
       </c>
       <c r="H19" s="6">
         <v>46371</v>
@@ -1058,22 +1058,22 @@
         <v>1768</v>
       </c>
       <c r="B20" s="3">
-        <v>40032</v>
+        <v>40035</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D20" s="3">
         <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F20" s="4">
-        <v>190</v>
+        <v>5</v>
       </c>
       <c r="G20" s="5">
-        <v>3.3</v>
+        <v>21</v>
       </c>
       <c r="H20" s="6">
         <v>46371</v>
@@ -1084,10 +1084,10 @@
         <v>1768</v>
       </c>
       <c r="B21" s="3">
-        <v>40033</v>
+        <v>40036</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D21" s="3">
         <v>9</v>
@@ -1096,10 +1096,10 @@
         <v>25</v>
       </c>
       <c r="F21" s="4">
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="G21" s="5">
-        <v>13.39</v>
+        <v>3.52</v>
       </c>
       <c r="H21" s="6">
         <v>46371</v>
@@ -1110,10 +1110,10 @@
         <v>1768</v>
       </c>
       <c r="B22" s="3">
-        <v>40034</v>
+        <v>40037</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D22" s="3">
         <v>9</v>
@@ -1122,10 +1122,10 @@
         <v>25</v>
       </c>
       <c r="F22" s="4">
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="G22" s="5">
-        <v>13.33</v>
+        <v>3.3</v>
       </c>
       <c r="H22" s="6">
         <v>46371</v>
@@ -1136,10 +1136,10 @@
         <v>1768</v>
       </c>
       <c r="B23" s="3">
-        <v>40035</v>
+        <v>40038</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D23" s="3">
         <v>9</v>
@@ -1148,10 +1148,10 @@
         <v>25</v>
       </c>
       <c r="F23" s="4">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="G23" s="5">
-        <v>21</v>
+        <v>2.54</v>
       </c>
       <c r="H23" s="6">
         <v>46371</v>
@@ -1162,10 +1162,10 @@
         <v>1768</v>
       </c>
       <c r="B24" s="3">
-        <v>40036</v>
+        <v>40039</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D24" s="3">
         <v>9</v>
@@ -1174,10 +1174,10 @@
         <v>25</v>
       </c>
       <c r="F24" s="4">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G24" s="5">
-        <v>3.52</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="H24" s="6">
         <v>46371</v>
@@ -1188,10 +1188,10 @@
         <v>1768</v>
       </c>
       <c r="B25" s="3">
-        <v>40037</v>
+        <v>40040</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D25" s="3">
         <v>9</v>
@@ -1200,90 +1200,12 @@
         <v>25</v>
       </c>
       <c r="F25" s="4">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G25" s="5">
-        <v>3.3</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="H25" s="6">
-        <v>46371</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B26" s="3">
-        <v>40038</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="3">
-        <v>9</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="4">
-        <v>200</v>
-      </c>
-      <c r="G26" s="5">
-        <v>2.54</v>
-      </c>
-      <c r="H26" s="6">
-        <v>46371</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B27" s="3">
-        <v>40039</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="3">
-        <v>9</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="4">
-        <v>200</v>
-      </c>
-      <c r="G27" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="H27" s="6">
-        <v>46371</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B28" s="3">
-        <v>40040</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="3">
-        <v>9</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="4">
-        <v>200</v>
-      </c>
-      <c r="G28" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="H28" s="6">
         <v>46371</v>
       </c>
     </row>

--- a/data-source/COMPRASQUIMICOS.xlsx
+++ b/data-source/COMPRASQUIMICOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\QUIMICOS-ANALISE\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5315D4-564D-431E-87FA-B056E0B89317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987E8947-A111-44A1-B4A1-CD636CE906CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="33">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -546,7 +546,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
@@ -634,7 +634,7 @@
         <v>1.75</v>
       </c>
       <c r="H3" s="6">
-        <v>46294</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -660,7 +660,7 @@
         <v>1.75</v>
       </c>
       <c r="H4" s="6">
-        <v>46325</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -680,13 +680,13 @@
         <v>14</v>
       </c>
       <c r="F5" s="4">
-        <v>2850</v>
+        <v>3800</v>
       </c>
       <c r="G5" s="5">
         <v>1.75</v>
       </c>
       <c r="H5" s="6">
-        <v>46356</v>
+        <v>46366</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -694,51 +694,51 @@
         <v>1617</v>
       </c>
       <c r="B6" s="3">
-        <v>8329</v>
+        <v>30218</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" s="3">
         <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4">
-        <v>3800</v>
+        <v>75</v>
       </c>
       <c r="G6" s="5">
-        <v>1.75</v>
+        <v>33</v>
       </c>
       <c r="H6" s="6">
-        <v>46366</v>
+        <v>46367</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>1617</v>
-      </c>
-      <c r="B7" s="3">
-        <v>30218</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="3">
-        <v>9</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="A7">
+        <v>1250</v>
+      </c>
+      <c r="B7">
+        <v>4478</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="4">
-        <v>75</v>
-      </c>
-      <c r="G7" s="5">
-        <v>33</v>
+        <v>1000</v>
+      </c>
+      <c r="G7">
+        <v>2.14</v>
       </c>
       <c r="H7" s="6">
-        <v>46367</v>
+        <v>46368</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -746,10 +746,10 @@
         <v>1250</v>
       </c>
       <c r="B8">
-        <v>4478</v>
+        <v>5797</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -761,10 +761,10 @@
         <v>1000</v>
       </c>
       <c r="G8">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="H8" s="6">
-        <v>46368</v>
+        <v>46369</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -772,10 +772,10 @@
         <v>1250</v>
       </c>
       <c r="B9">
-        <v>5797</v>
+        <v>6506</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -787,36 +787,36 @@
         <v>1000</v>
       </c>
       <c r="G9">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="H9" s="6">
-        <v>46369</v>
+        <v>46370</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1250</v>
-      </c>
-      <c r="B10">
-        <v>6506</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
+      <c r="A10" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B10" s="3">
+        <v>11370</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F10" s="4">
-        <v>1000</v>
-      </c>
-      <c r="G10">
-        <v>2.23</v>
+        <v>6660</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1.97</v>
       </c>
       <c r="H10" s="6">
-        <v>46370</v>
+        <v>46371</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -824,10 +824,10 @@
         <v>1768</v>
       </c>
       <c r="B11" s="3">
-        <v>11370</v>
+        <v>11374</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D11" s="3">
         <v>9</v>
@@ -836,10 +836,10 @@
         <v>17</v>
       </c>
       <c r="F11" s="4">
-        <v>6660</v>
+        <v>3060</v>
       </c>
       <c r="G11" s="5">
-        <v>1.97</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H11" s="6">
         <v>46371</v>
@@ -850,10 +850,10 @@
         <v>1768</v>
       </c>
       <c r="B12" s="3">
-        <v>11374</v>
+        <v>11379</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3">
         <v>9</v>
@@ -865,7 +865,7 @@
         <v>3060</v>
       </c>
       <c r="G12" s="5">
-        <v>4.9000000000000004</v>
+        <v>5.13</v>
       </c>
       <c r="H12" s="6">
         <v>46371</v>
@@ -876,10 +876,10 @@
         <v>1768</v>
       </c>
       <c r="B13" s="3">
-        <v>11379</v>
+        <v>11380</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="3">
         <v>9</v>
@@ -891,7 +891,7 @@
         <v>3060</v>
       </c>
       <c r="G13" s="5">
-        <v>5.13</v>
+        <v>3.13</v>
       </c>
       <c r="H13" s="6">
         <v>46371</v>
@@ -902,10 +902,10 @@
         <v>1768</v>
       </c>
       <c r="B14" s="3">
-        <v>11380</v>
+        <v>16336</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="3">
         <v>9</v>
@@ -914,10 +914,10 @@
         <v>17</v>
       </c>
       <c r="F14" s="4">
-        <v>3060</v>
+        <v>5040</v>
       </c>
       <c r="G14" s="5">
-        <v>3.13</v>
+        <v>1.97</v>
       </c>
       <c r="H14" s="6">
         <v>46371</v>
@@ -928,10 +928,10 @@
         <v>1768</v>
       </c>
       <c r="B15" s="3">
-        <v>16336</v>
+        <v>16684</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="3">
         <v>9</v>
@@ -940,10 +940,10 @@
         <v>17</v>
       </c>
       <c r="F15" s="4">
-        <v>5040</v>
+        <v>1080</v>
       </c>
       <c r="G15" s="5">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="H15" s="6">
         <v>46371</v>
@@ -954,10 +954,10 @@
         <v>1768</v>
       </c>
       <c r="B16" s="3">
-        <v>16684</v>
+        <v>40032</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="3">
         <v>9</v>
@@ -966,10 +966,10 @@
         <v>17</v>
       </c>
       <c r="F16" s="4">
-        <v>1080</v>
+        <v>190</v>
       </c>
       <c r="G16" s="5">
-        <v>2.16</v>
+        <v>3.3</v>
       </c>
       <c r="H16" s="6">
         <v>46371</v>
@@ -980,22 +980,22 @@
         <v>1768</v>
       </c>
       <c r="B17" s="3">
-        <v>40032</v>
+        <v>40033</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" s="3">
         <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F17" s="4">
-        <v>190</v>
+        <v>5</v>
       </c>
       <c r="G17" s="5">
-        <v>3.3</v>
+        <v>13.39</v>
       </c>
       <c r="H17" s="6">
         <v>46371</v>
@@ -1006,10 +1006,10 @@
         <v>1768</v>
       </c>
       <c r="B18" s="3">
-        <v>40033</v>
+        <v>40034</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D18" s="3">
         <v>9</v>
@@ -1021,7 +1021,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="5">
-        <v>13.39</v>
+        <v>13.33</v>
       </c>
       <c r="H18" s="6">
         <v>46371</v>
@@ -1032,10 +1032,10 @@
         <v>1768</v>
       </c>
       <c r="B19" s="3">
-        <v>40034</v>
+        <v>40035</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="3">
         <v>9</v>
@@ -1047,7 +1047,7 @@
         <v>5</v>
       </c>
       <c r="G19" s="5">
-        <v>13.33</v>
+        <v>21</v>
       </c>
       <c r="H19" s="6">
         <v>46371</v>
@@ -1058,10 +1058,10 @@
         <v>1768</v>
       </c>
       <c r="B20" s="3">
-        <v>40035</v>
+        <v>40036</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" s="3">
         <v>9</v>
@@ -1070,10 +1070,10 @@
         <v>25</v>
       </c>
       <c r="F20" s="4">
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="G20" s="5">
-        <v>21</v>
+        <v>3.52</v>
       </c>
       <c r="H20" s="6">
         <v>46371</v>
@@ -1084,10 +1084,10 @@
         <v>1768</v>
       </c>
       <c r="B21" s="3">
-        <v>40036</v>
+        <v>40037</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" s="3">
         <v>9</v>
@@ -1099,7 +1099,7 @@
         <v>190</v>
       </c>
       <c r="G21" s="5">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="H21" s="6">
         <v>46371</v>
@@ -1110,10 +1110,10 @@
         <v>1768</v>
       </c>
       <c r="B22" s="3">
-        <v>40037</v>
+        <v>40038</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22" s="3">
         <v>9</v>
@@ -1122,10 +1122,10 @@
         <v>25</v>
       </c>
       <c r="F22" s="4">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G22" s="5">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="H22" s="6">
         <v>46371</v>
@@ -1136,10 +1136,10 @@
         <v>1768</v>
       </c>
       <c r="B23" s="3">
-        <v>40038</v>
+        <v>40039</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" s="3">
         <v>9</v>
@@ -1151,7 +1151,7 @@
         <v>200</v>
       </c>
       <c r="G23" s="5">
-        <v>2.54</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="H23" s="6">
         <v>46371</v>
@@ -1162,10 +1162,10 @@
         <v>1768</v>
       </c>
       <c r="B24" s="3">
-        <v>40039</v>
+        <v>40040</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24" s="3">
         <v>9</v>
@@ -1180,32 +1180,6 @@
         <v>2.0699999999999998</v>
       </c>
       <c r="H24" s="6">
-        <v>46371</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B25" s="3">
-        <v>40040</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="3">
-        <v>9</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="4">
-        <v>200</v>
-      </c>
-      <c r="G25" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="H25" s="6">
         <v>46371</v>
       </c>
     </row>

--- a/data-source/COMPRASQUIMICOS.xlsx
+++ b/data-source/COMPRASQUIMICOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987E8947-A111-44A1-B4A1-CD636CE906CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{2A5315D4-564D-431E-87FA-B056E0B89317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B500097-1586-45EE-B8F5-53DC7F3F42FE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>RESINA JF-HSY-BY100 - AMERICA ASIA</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>RESINA JF-HSY-BY400 - AMERICA ASIA</t>
@@ -161,7 +158,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -171,6 +168,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -201,14 +204,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,45 +564,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1667</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>11849</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="2">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="4">
@@ -612,19 +616,19 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>1617</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>8329</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="2">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="4">
@@ -638,19 +642,19 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>1617</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>8329</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="2">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="4">
@@ -664,19 +668,19 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>1617</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>8329</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="3">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="2">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="4">
@@ -690,23 +694,23 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>1617</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="A6" s="2">
+        <v>1727</v>
+      </c>
+      <c r="B6" s="2">
         <v>30218</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="2">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="4">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G6" s="5">
         <v>33</v>
@@ -716,25 +720,25 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1250</v>
-      </c>
-      <c r="B7">
+      <c r="A7" s="7">
+        <v>1738</v>
+      </c>
+      <c r="B7" s="7">
         <v>4478</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="C7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7">
+        <v>9</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="4">
         <v>1000</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="7">
         <v>2.14</v>
       </c>
       <c r="H7" s="6">
@@ -742,25 +746,25 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1250</v>
-      </c>
-      <c r="B8">
+      <c r="A8" s="7">
+        <v>1738</v>
+      </c>
+      <c r="B8" s="7">
         <v>5797</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D8">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D8" s="7">
+        <v>9</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="4">
         <v>1000</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="7">
         <v>1.86</v>
       </c>
       <c r="H8" s="6">
@@ -768,25 +772,25 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1250</v>
-      </c>
-      <c r="B9">
+      <c r="A9" s="7">
+        <v>1738</v>
+      </c>
+      <c r="B9" s="7">
         <v>6506</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D9">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="7">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F9" s="4">
         <v>1000</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="7">
         <v>2.23</v>
       </c>
       <c r="H9" s="6">
@@ -794,19 +798,19 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B10" s="2">
         <v>11370</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="3">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="D10" s="2">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="4">
@@ -820,19 +824,19 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B11" s="3">
+      <c r="A11" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B11" s="2">
         <v>11374</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="3">
-        <v>9</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="2">
+        <v>9</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="4">
@@ -846,19 +850,19 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B12" s="3">
+      <c r="A12" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B12" s="2">
         <v>11379</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="3">
-        <v>9</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="2">
+        <v>9</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="4">
@@ -872,19 +876,19 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B13" s="3">
+      <c r="A13" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B13" s="2">
         <v>11380</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="3">
-        <v>9</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="2">
+        <v>9</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="4">
@@ -898,19 +902,19 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="A14" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B14" s="2">
         <v>16336</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="3">
-        <v>9</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="2">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="4">
@@ -924,19 +928,19 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B15" s="3">
+      <c r="A15" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B15" s="2">
         <v>16684</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="3">
-        <v>9</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="2">
+        <v>9</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="4">
@@ -950,19 +954,19 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B16" s="3">
+      <c r="A16" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B16" s="2">
         <v>40032</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="3">
-        <v>9</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" s="2">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F16" s="4">
@@ -976,20 +980,20 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B17" s="3">
+      <c r="A17" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B17" s="2">
         <v>40033</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="3">
-        <v>9</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>25</v>
+      <c r="D17" s="2">
+        <v>9</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F17" s="4">
         <v>5</v>
@@ -1002,20 +1006,20 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B18" s="3">
+      <c r="A18" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B18" s="2">
         <v>40034</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="3">
-        <v>9</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>25</v>
+      </c>
+      <c r="D18" s="2">
+        <v>9</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F18" s="4">
         <v>5</v>
@@ -1028,20 +1032,20 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B19" s="3">
+      <c r="A19" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B19" s="2">
         <v>40035</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="3">
-        <v>9</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>25</v>
+      <c r="C19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="2">
+        <v>9</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F19" s="4">
         <v>5</v>
@@ -1054,20 +1058,20 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B20" s="3">
+      <c r="A20" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B20" s="2">
         <v>40036</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="3">
-        <v>9</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>25</v>
+      <c r="C20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="2">
+        <v>9</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F20" s="4">
         <v>190</v>
@@ -1080,20 +1084,20 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B21" s="3">
+      <c r="A21" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B21" s="2">
         <v>40037</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="3">
-        <v>9</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>25</v>
+      <c r="C21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="2">
+        <v>9</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F21" s="4">
         <v>190</v>
@@ -1106,20 +1110,20 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="A22" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B22" s="2">
         <v>40038</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="3">
-        <v>9</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>25</v>
+      <c r="C22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="2">
+        <v>9</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F22" s="4">
         <v>200</v>
@@ -1132,20 +1136,20 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B23" s="3">
+      <c r="A23" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B23" s="2">
         <v>40039</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="3">
-        <v>9</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>25</v>
+      <c r="C23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="2">
+        <v>9</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F23" s="4">
         <v>200</v>
@@ -1158,20 +1162,20 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>1768</v>
-      </c>
-      <c r="B24" s="3">
+      <c r="A24" s="2">
+        <v>1768</v>
+      </c>
+      <c r="B24" s="2">
         <v>40040</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="3">
-        <v>9</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>25</v>
+      <c r="C24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="2">
+        <v>9</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F24" s="4">
         <v>200</v>

--- a/data-source/COMPRASQUIMICOS.xlsx
+++ b/data-source/COMPRASQUIMICOS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{2A5315D4-564D-431E-87FA-B056E0B89317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B500097-1586-45EE-B8F5-53DC7F3F42FE}"/>
@@ -156,6 +156,7 @@
       <sz val="11"/>
       <color rgb="FF800000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
